--- a/data/ai_teams.xlsx
+++ b/data/ai_teams.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -478,13 +478,13 @@
         <v>ai_team_001</v>
       </c>
       <c r="B2" t="str">
-        <v>新手挑战队</v>
+        <v>菜鸟练习队</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="str">
-        <v>gk_001</v>
+        <v>ai_gk_01</v>
       </c>
       <c r="E2">
         <v>0.05</v>
@@ -493,37 +493,37 @@
         <v>0.5</v>
       </c>
       <c r="G2" t="str">
-        <v>df_001</v>
+        <v>ai_df_01</v>
       </c>
       <c r="H2">
         <v>0.2</v>
       </c>
       <c r="I2">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="str">
-        <v>df_002</v>
+        <v>ai_mf_01</v>
       </c>
       <c r="K2">
-        <v>0.2</v>
+        <v>0.42</v>
       </c>
       <c r="L2">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="M2" t="str">
-        <v>mf_001</v>
+        <v>ai_mf_02</v>
       </c>
       <c r="N2">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="O2">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="P2" t="str">
-        <v>fw_002</v>
+        <v>ai_fw_01</v>
       </c>
       <c r="Q2">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="R2">
         <v>0.5</v>
@@ -552,13 +552,13 @@
         <v>ai_team_002</v>
       </c>
       <c r="B3" t="str">
-        <v>实力对手</v>
+        <v>街头霸王队</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="str">
-        <v>gk_001</v>
+        <v>ai_gk_01</v>
       </c>
       <c r="E3">
         <v>0.05</v>
@@ -567,7 +567,7 @@
         <v>0.5</v>
       </c>
       <c r="G3" t="str">
-        <v>df_001</v>
+        <v>ai_df_01</v>
       </c>
       <c r="H3">
         <v>0.2</v>
@@ -576,7 +576,7 @@
         <v>0.3</v>
       </c>
       <c r="J3" t="str">
-        <v>df_002</v>
+        <v>ai_df_02</v>
       </c>
       <c r="K3">
         <v>0.2</v>
@@ -585,28 +585,28 @@
         <v>0.7</v>
       </c>
       <c r="M3" t="str">
-        <v>mf_001</v>
+        <v>ai_mf_02</v>
       </c>
       <c r="N3">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="O3">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="P3" t="str">
-        <v>mf_002</v>
+        <v>ai_mf_03</v>
       </c>
       <c r="Q3">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="R3">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="S3" t="str">
-        <v>fw_001</v>
+        <v>ai_fw_02</v>
       </c>
       <c r="T3">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="U3">
         <v>0.5</v>
@@ -626,13 +626,13 @@
         <v>ai_team_003</v>
       </c>
       <c r="B4" t="str">
-        <v>精英劲旅</v>
+        <v>武当少年队</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="str">
-        <v>gk_001</v>
+        <v>ai_gk_02</v>
       </c>
       <c r="E4">
         <v>0.05</v>
@@ -641,7 +641,7 @@
         <v>0.5</v>
       </c>
       <c r="G4" t="str">
-        <v>df_001</v>
+        <v>ai_df_02</v>
       </c>
       <c r="H4">
         <v>0.2</v>
@@ -650,7 +650,7 @@
         <v>0.3</v>
       </c>
       <c r="J4" t="str">
-        <v>df_002</v>
+        <v>ai_df_03</v>
       </c>
       <c r="K4">
         <v>0.2</v>
@@ -659,45 +659,193 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="str">
-        <v>mf_001</v>
+        <v>ai_mf_03</v>
       </c>
       <c r="N4">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="O4">
         <v>0.3</v>
       </c>
       <c r="P4" t="str">
-        <v>mf_002</v>
+        <v>ai_mf_04</v>
       </c>
       <c r="Q4">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="R4">
         <v>0.7</v>
       </c>
       <c r="S4" t="str">
-        <v>fw_001</v>
+        <v>ai_fw_02</v>
       </c>
       <c r="T4">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="U4">
         <v>0.35</v>
       </c>
       <c r="V4" t="str">
-        <v>fw_003</v>
+        <v>ai_fw_03</v>
       </c>
       <c r="W4">
+        <v>0.68</v>
+      </c>
+      <c r="X4">
         <v>0.65</v>
       </c>
-      <c r="X4">
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ai_team_004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>少林精英队</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="str">
+        <v>ai_gk_02</v>
+      </c>
+      <c r="E5">
+        <v>0.05</v>
+      </c>
+      <c r="F5">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="str">
+        <v>ai_df_03</v>
+      </c>
+      <c r="H5">
+        <v>0.2</v>
+      </c>
+      <c r="I5">
+        <v>0.3</v>
+      </c>
+      <c r="J5" t="str">
+        <v>ai_df_04</v>
+      </c>
+      <c r="K5">
+        <v>0.2</v>
+      </c>
+      <c r="L5">
+        <v>0.7</v>
+      </c>
+      <c r="M5" t="str">
+        <v>ai_mf_04</v>
+      </c>
+      <c r="N5">
+        <v>0.42</v>
+      </c>
+      <c r="O5">
+        <v>0.3</v>
+      </c>
+      <c r="P5" t="str">
+        <v>ai_mf_05</v>
+      </c>
+      <c r="Q5">
+        <v>0.42</v>
+      </c>
+      <c r="R5">
+        <v>0.7</v>
+      </c>
+      <c r="S5" t="str">
+        <v>ai_fw_03</v>
+      </c>
+      <c r="T5">
+        <v>0.68</v>
+      </c>
+      <c r="U5">
+        <v>0.35</v>
+      </c>
+      <c r="V5" t="str">
+        <v>ai_fw_04</v>
+      </c>
+      <c r="W5">
+        <v>0.68</v>
+      </c>
+      <c r="X5">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ai_team_005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>天下第一队</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="str">
+        <v>ai_gk_03</v>
+      </c>
+      <c r="E6">
+        <v>0.05</v>
+      </c>
+      <c r="F6">
+        <v>0.5</v>
+      </c>
+      <c r="G6" t="str">
+        <v>ai_df_04</v>
+      </c>
+      <c r="H6">
+        <v>0.2</v>
+      </c>
+      <c r="I6">
+        <v>0.3</v>
+      </c>
+      <c r="J6" t="str">
+        <v>ai_df_05</v>
+      </c>
+      <c r="K6">
+        <v>0.2</v>
+      </c>
+      <c r="L6">
+        <v>0.7</v>
+      </c>
+      <c r="M6" t="str">
+        <v>ai_mf_05</v>
+      </c>
+      <c r="N6">
+        <v>0.42</v>
+      </c>
+      <c r="O6">
+        <v>0.3</v>
+      </c>
+      <c r="P6" t="str">
+        <v>ai_mf_04</v>
+      </c>
+      <c r="Q6">
+        <v>0.42</v>
+      </c>
+      <c r="R6">
+        <v>0.7</v>
+      </c>
+      <c r="S6" t="str">
+        <v>ai_fw_04</v>
+      </c>
+      <c r="T6">
+        <v>0.68</v>
+      </c>
+      <c r="U6">
+        <v>0.35</v>
+      </c>
+      <c r="V6" t="str">
+        <v>ai_fw_05</v>
+      </c>
+      <c r="W6">
+        <v>0.68</v>
+      </c>
+      <c r="X6">
         <v>0.65</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X6"/>
   </ignoredErrors>
 </worksheet>
 </file>